--- a/ListadoLab.XLSX
+++ b/ListadoLab.XLSX
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\germa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Desarrollo\Python\Correlaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A262DEAF-5488-420B-A322-A3F85C4E849A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91FF245-D0D6-4C7F-8026-8324A1415B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -721,9 +721,6 @@
     <t>Cohesión KPa con drenaje</t>
   </si>
   <si>
-    <t>Tipo Ensayo sin drenaje</t>
-  </si>
-  <si>
     <t>Indice de Poros</t>
   </si>
   <si>
@@ -761,6 +758,9 @@
   </si>
   <si>
     <t>Cohesión KPa residual</t>
+  </si>
+  <si>
+    <t>Tipo Ensayo residuales</t>
   </si>
 </sst>
 </file>
@@ -1332,13 +1332,13 @@
         <v>232</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="AP1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="AQ1" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>199</v>
@@ -1350,37 +1350,37 @@
         <v>201</v>
       </c>
       <c r="AU1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.2">
